--- a/applications/exercise_study/negative/seq_neg_exercise.xlsx
+++ b/applications/exercise_study/negative/seq_neg_exercise.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Extreme SSD/Metformin_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/exercise_study/negative/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAC3463-4E60-184A-ACAC-3B9B7039A3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F844EBEF-81BD-4D42-82D1-0300CC072C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3520" yWindow="1580" windowWidth="25720" windowHeight="15720" xr2:uid="{B0E1915D-E88D-4422-93FC-8C65A0CDB4AB}"/>
   </bookViews>
@@ -56,9 +56,6 @@
     <t>sample_name</t>
   </si>
   <si>
-    <t>inj_no</t>
-  </si>
-  <si>
     <t>QC_1</t>
   </si>
   <si>
@@ -1371,6 +1368,9 @@
   </si>
   <si>
     <t>Timepoint</t>
+  </si>
+  <si>
+    <t>injection_index</t>
   </si>
 </sst>
 </file>
@@ -1775,9 +1775,9 @@
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>443</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -1792,10 +1792,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -1803,10 +1803,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>2</v>
@@ -1826,13 +1826,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1849,13 +1849,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1872,13 +1872,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1895,13 +1895,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1918,13 +1918,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1941,10 +1941,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>2</v>
@@ -1964,13 +1964,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1987,13 +1987,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -2010,13 +2010,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2033,13 +2033,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2056,13 +2056,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -2079,10 +2079,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>2</v>
@@ -2102,13 +2102,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2125,13 +2125,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -2148,13 +2148,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2171,13 +2171,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2217,10 +2217,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>2</v>
@@ -2240,13 +2240,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2263,13 +2263,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2286,13 +2286,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -2309,13 +2309,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -2332,13 +2332,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -2355,10 +2355,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>2</v>
@@ -2378,13 +2378,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2401,13 +2401,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2424,13 +2424,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -2447,13 +2447,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2470,13 +2470,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -2493,10 +2493,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>2</v>
@@ -2516,13 +2516,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -2539,13 +2539,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -2562,13 +2562,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -2585,13 +2585,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -2608,13 +2608,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -2631,10 +2631,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>2</v>
@@ -2654,13 +2654,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -2677,13 +2677,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -2700,13 +2700,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -2723,13 +2723,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -2746,13 +2746,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -2769,10 +2769,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>2</v>
@@ -2792,13 +2792,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -2815,13 +2815,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -2838,13 +2838,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -2861,13 +2861,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -2884,13 +2884,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -2907,10 +2907,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>2</v>
@@ -2930,13 +2930,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -2953,13 +2953,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -2976,13 +2976,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -2999,13 +2999,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -3022,13 +3022,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -3045,10 +3045,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>2</v>
@@ -3068,13 +3068,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -3091,13 +3091,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -3114,13 +3114,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -3137,13 +3137,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -3160,13 +3160,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -3183,10 +3183,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C62" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>2</v>
@@ -3206,13 +3206,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -3229,13 +3229,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C64" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E64">
         <v>1</v>
@@ -3252,13 +3252,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -3275,13 +3275,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C66" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -3298,13 +3298,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C67" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E67">
         <v>1</v>
@@ -3321,10 +3321,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C68" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>2</v>
@@ -3344,13 +3344,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C69" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -3367,13 +3367,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C70" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -3390,13 +3390,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -3413,13 +3413,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C72" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -3436,13 +3436,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -3459,10 +3459,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C74" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>2</v>
@@ -3482,13 +3482,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C75" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -3505,13 +3505,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C76" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E76">
         <v>1</v>
@@ -3528,13 +3528,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E77">
         <v>1</v>
@@ -3551,13 +3551,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C78" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -3574,13 +3574,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C79" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E79">
         <v>1</v>
@@ -3597,10 +3597,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C80" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>2</v>
@@ -3620,13 +3620,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C81" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E81">
         <v>1</v>
@@ -3643,13 +3643,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C82" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E82">
         <v>1</v>
@@ -3666,13 +3666,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C83" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E83">
         <v>1</v>
@@ -3689,13 +3689,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C84" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E84">
         <v>1</v>
@@ -3712,13 +3712,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C85" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E85">
         <v>1</v>
@@ -3735,10 +3735,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C86" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>2</v>
@@ -3758,13 +3758,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C87" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E87">
         <v>1</v>
@@ -3781,13 +3781,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C88" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E88">
         <v>1</v>
@@ -3804,13 +3804,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C89" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E89">
         <v>1</v>
@@ -3827,13 +3827,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C90" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E90">
         <v>1</v>
@@ -3850,13 +3850,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C91" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E91">
         <v>1</v>
@@ -3873,10 +3873,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C92" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>2</v>
@@ -3896,13 +3896,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C93" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E93">
         <v>1</v>
@@ -3919,13 +3919,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C94" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -3942,13 +3942,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C95" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -3965,13 +3965,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C96" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E96">
         <v>1</v>
@@ -3988,13 +3988,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C97" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -4011,10 +4011,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C98" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>2</v>
@@ -4034,13 +4034,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C99" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -4057,13 +4057,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -4080,13 +4080,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C101" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E101">
         <v>1</v>
@@ -4103,13 +4103,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C102" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E102">
         <v>1</v>
@@ -4126,13 +4126,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C103" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E103">
         <v>1</v>
@@ -4149,10 +4149,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C104" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>2</v>
@@ -4172,13 +4172,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C105" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E105">
         <v>1</v>
@@ -4195,13 +4195,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C106" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E106">
         <v>1</v>
@@ -4218,13 +4218,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C107" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E107">
         <v>1</v>
@@ -4241,13 +4241,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C108" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E108">
         <v>1</v>
@@ -4264,13 +4264,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C109" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E109">
         <v>1</v>
@@ -4287,10 +4287,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C110" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>2</v>
@@ -4310,13 +4310,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C111" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E111">
         <v>1</v>
@@ -4333,13 +4333,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C112" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E112">
         <v>1</v>
@@ -4356,13 +4356,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C113" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E113">
         <v>1</v>
@@ -4379,13 +4379,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C114" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E114">
         <v>1</v>
@@ -4402,13 +4402,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C115" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E115">
         <v>1</v>
@@ -4425,10 +4425,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C116" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>2</v>
@@ -4448,13 +4448,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C117" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E117">
         <v>1</v>
@@ -4471,13 +4471,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C118" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -4494,13 +4494,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C119" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E119">
         <v>1</v>
@@ -4517,13 +4517,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C120" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E120">
         <v>1</v>
@@ -4540,13 +4540,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C121" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -4563,10 +4563,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C122" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>2</v>
@@ -4586,13 +4586,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C123" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -4609,13 +4609,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C124" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E124">
         <v>1</v>
@@ -4632,13 +4632,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C125" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E125">
         <v>1</v>
@@ -4655,13 +4655,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C126" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E126">
         <v>1</v>
@@ -4678,13 +4678,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C127" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E127">
         <v>1</v>
@@ -4701,10 +4701,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C128" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>2</v>
@@ -4724,13 +4724,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C129" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E129">
         <v>1</v>
@@ -4747,13 +4747,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C130" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E130">
         <v>1</v>
@@ -4770,13 +4770,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C131" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E131">
         <v>1</v>
@@ -4793,13 +4793,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C132" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E132">
         <v>1</v>
@@ -4816,13 +4816,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C133" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -4839,10 +4839,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C134" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>2</v>
@@ -4862,13 +4862,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C135" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -4885,13 +4885,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C136" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -4908,13 +4908,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C137" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -4931,13 +4931,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C138" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -4954,13 +4954,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C139" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -4977,10 +4977,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C140" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>2</v>
@@ -5000,13 +5000,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C141" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E141">
         <v>1</v>
@@ -5023,13 +5023,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C142" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E142">
         <v>1</v>
@@ -5046,13 +5046,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C143" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E143">
         <v>1</v>
@@ -5069,13 +5069,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C144" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -5092,13 +5092,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C145" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E145">
         <v>1</v>
@@ -5115,10 +5115,10 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C146" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>2</v>
@@ -5138,13 +5138,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C147" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -5161,13 +5161,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C148" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E148">
         <v>1</v>
@@ -5184,13 +5184,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C149" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E149">
         <v>1</v>
@@ -5207,13 +5207,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C150" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E150">
         <v>1</v>
@@ -5230,13 +5230,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C151" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -5253,10 +5253,10 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C152" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>2</v>
@@ -5276,13 +5276,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C153" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E153">
         <v>1</v>
@@ -5299,13 +5299,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C154" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E154">
         <v>1</v>
@@ -5322,13 +5322,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C155" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E155">
         <v>1</v>
@@ -5345,13 +5345,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C156" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -5368,13 +5368,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C157" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E157">
         <v>1</v>
@@ -5391,10 +5391,10 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C158" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>2</v>
@@ -5414,13 +5414,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C159" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E159">
         <v>1</v>
@@ -5437,13 +5437,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C160" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E160">
         <v>1</v>
@@ -5460,13 +5460,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C161" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E161">
         <v>1</v>
@@ -5483,13 +5483,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C162" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E162">
         <v>1</v>
@@ -5506,13 +5506,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C163" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E163">
         <v>1</v>
@@ -5529,10 +5529,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C164" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>2</v>
@@ -5552,13 +5552,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C165" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E165">
         <v>1</v>
@@ -5575,13 +5575,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C166" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E166">
         <v>1</v>
@@ -5598,13 +5598,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C167" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -5621,13 +5621,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C168" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E168">
         <v>1</v>
@@ -5644,13 +5644,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C169" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E169">
         <v>1</v>
@@ -5667,10 +5667,10 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C170" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>2</v>
@@ -5690,13 +5690,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C171" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E171">
         <v>1</v>
@@ -5713,13 +5713,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C172" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E172">
         <v>1</v>
@@ -5736,13 +5736,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C173" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -5759,13 +5759,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C174" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E174">
         <v>1</v>
@@ -5782,13 +5782,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C175" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E175">
         <v>1</v>
@@ -5805,10 +5805,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C176" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>2</v>
@@ -5828,13 +5828,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C177" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E177">
         <v>1</v>
@@ -5851,13 +5851,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C178" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E178">
         <v>1</v>
@@ -5874,13 +5874,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C179" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E179">
         <v>1</v>
@@ -5897,13 +5897,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C180" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E180">
         <v>1</v>
@@ -5920,13 +5920,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C181" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E181">
         <v>1</v>
@@ -5943,10 +5943,10 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C182" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>2</v>
@@ -5966,13 +5966,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C183" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E183">
         <v>1</v>
@@ -5989,13 +5989,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C184" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E184">
         <v>1</v>
@@ -6012,13 +6012,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C185" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E185">
         <v>1</v>
@@ -6035,13 +6035,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C186" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E186">
         <v>1</v>
@@ -6058,13 +6058,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C187" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E187">
         <v>1</v>
@@ -6081,10 +6081,10 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C188" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>2</v>
@@ -6104,13 +6104,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C189" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E189">
         <v>1</v>
@@ -6127,13 +6127,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C190" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E190">
         <v>1</v>
@@ -6150,13 +6150,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C191" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E191">
         <v>1</v>
@@ -6173,13 +6173,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C192" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E192">
         <v>1</v>
@@ -6196,13 +6196,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C193" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E193">
         <v>1</v>
@@ -6219,10 +6219,10 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C194" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>2</v>
@@ -6242,13 +6242,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C195" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E195">
         <v>1</v>
@@ -6265,13 +6265,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C196" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E196">
         <v>1</v>
@@ -6288,13 +6288,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C197" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E197">
         <v>1</v>
@@ -6311,13 +6311,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C198" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E198">
         <v>1</v>
@@ -6334,13 +6334,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C199" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E199">
         <v>1</v>
@@ -6357,10 +6357,10 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C200" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>2</v>
@@ -6380,13 +6380,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C201" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E201">
         <v>1</v>
@@ -6403,13 +6403,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C202" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E202">
         <v>1</v>
@@ -6426,13 +6426,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C203" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E203">
         <v>1</v>
@@ -6449,13 +6449,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C204" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E204">
         <v>1</v>
@@ -6472,13 +6472,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C205" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E205">
         <v>1</v>
@@ -6495,10 +6495,10 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C206" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>2</v>
@@ -6518,13 +6518,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C207" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E207">
         <v>1</v>
@@ -6541,13 +6541,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C208" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E208">
         <v>1</v>
@@ -6564,13 +6564,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C209" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E209">
         <v>1</v>
@@ -6587,13 +6587,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C210" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E210">
         <v>1</v>
@@ -6610,13 +6610,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C211" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E211">
         <v>1</v>
@@ -6633,10 +6633,10 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C212" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>2</v>
@@ -6656,13 +6656,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C213" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E213">
         <v>1</v>
@@ -6679,13 +6679,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C214" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E214">
         <v>1</v>
@@ -6702,13 +6702,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C215" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E215">
         <v>1</v>
@@ -6725,13 +6725,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C216" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E216">
         <v>1</v>
@@ -6748,13 +6748,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C217" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E217">
         <v>1</v>
@@ -6771,10 +6771,10 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C218" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>2</v>

--- a/applications/exercise_study/negative/seq_neg_exercise.xlsx
+++ b/applications/exercise_study/negative/seq_neg_exercise.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/exercise_study/negative/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F844EBEF-81BD-4D42-82D1-0300CC072C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540C4787-B6FA-514B-8BB1-F6B70CD248A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3520" yWindow="1580" windowWidth="25720" windowHeight="15720" xr2:uid="{B0E1915D-E88D-4422-93FC-8C65A0CDB4AB}"/>
   </bookViews>
@@ -707,657 +707,6 @@
     <t>QC_37</t>
   </si>
   <si>
-    <t>A1_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A1_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A1_10_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A1_11_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A1_12_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A1_13_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A1_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A1_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A1_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A1_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A1_6_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A1_7_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A1_8_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A1_9_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_10_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_11_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_12_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_13_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_6_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_7_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_8_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A2_9_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_10_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_11_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_12_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_13_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_6_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_7_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_8_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A3_9_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_10_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_11_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_12_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_13_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_6_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_7_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_8_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A4_9_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_10_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_11_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_12_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_13_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_6_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_7_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_8_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A5_9_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_10_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_11_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_12_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_13_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_6_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_7_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_8_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A6_9_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_10_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_11_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_12_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_13_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_6_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_7_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_8_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A7_9_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_10_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_11_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_12_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_13_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_6_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_7_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_8_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A8_9_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_10_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_11_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_12_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_13_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_6_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_7_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_8_NEG.mzML</t>
-  </si>
-  <si>
-    <t>A9_9_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C1_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C1_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C1_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C1_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C1_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C1_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C2_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C2_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C2_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C2_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C2_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C2_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C3_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C3_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C3_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C3_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C3_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C3_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C4_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C4_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C4_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C4_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C4_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C4_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C5_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C5_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C5_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C5_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C5_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C5_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C6_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C6_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C6_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C6_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C6_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C6_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C7_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C7_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C7_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C7_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C7_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C7_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C8_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C8_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C8_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C8_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C8_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C8_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C9_0_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C9_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C9_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C9_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C9_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>C9_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_1_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_10_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_11_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_12_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_13_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_14_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_15_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_16_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_17_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_18_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_19_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_2_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_20_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_21_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_22_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_23_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_24_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_25_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_27_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_28_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_29_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_3_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_30_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_31_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_32_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_33_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_34_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_35_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_36_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_37_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_4_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_5_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_6_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_7_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_8_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_9_NEG.mzML</t>
-  </si>
-  <si>
-    <t>QC_26_NEG.mzML</t>
-  </si>
-  <si>
     <t>Exercise</t>
   </si>
   <si>
@@ -1371,6 +720,657 @@
   </si>
   <si>
     <t>injection_index</t>
+  </si>
+  <si>
+    <t>QC_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_3_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_8_N.mzML</t>
+  </si>
+  <si>
+    <t>C1_3_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_2_N.mzML</t>
+  </si>
+  <si>
+    <t>C1_5_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_11_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_6_N.mzML</t>
+  </si>
+  <si>
+    <t>C1_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_13_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_9_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_3_N.mzML</t>
+  </si>
+  <si>
+    <t>C1_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_4_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_1_N.mzML</t>
+  </si>
+  <si>
+    <t>C1_4_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_0_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_4_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_5_N.mzML</t>
+  </si>
+  <si>
+    <t>C1_0_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_12_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_10_N.mzML</t>
+  </si>
+  <si>
+    <t>A1_7_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_5_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_9_N.mzML</t>
+  </si>
+  <si>
+    <t>C2_3_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_11_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_7_N.mzML</t>
+  </si>
+  <si>
+    <t>C2_0_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_6_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_8_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_1_N.mzML</t>
+  </si>
+  <si>
+    <t>C2_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_13_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_2_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_7_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_0_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_10_N.mzML</t>
+  </si>
+  <si>
+    <t>C2_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_12_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_6_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_8_N.mzML</t>
+  </si>
+  <si>
+    <t>C2_4_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_5_N.mzML</t>
+  </si>
+  <si>
+    <t>C2_5_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_3_N.mzML</t>
+  </si>
+  <si>
+    <t>A2_4_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_9_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_6_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_10_N.mzML</t>
+  </si>
+  <si>
+    <t>C3_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_12_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_3_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_10_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_5_N.mzML</t>
+  </si>
+  <si>
+    <t>C3_4_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_9_N.mzML</t>
+  </si>
+  <si>
+    <t>C3_0_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_11_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_7_N.mzML</t>
+  </si>
+  <si>
+    <t>C3_3_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_11_N.mzML</t>
+  </si>
+  <si>
+    <t>C3_5_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_12_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_0_N.mzML</t>
+  </si>
+  <si>
+    <t>C3_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_4_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_13_N.mzML</t>
+  </si>
+  <si>
+    <t>A3_8_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_13_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_5_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_9_N.mzML</t>
+  </si>
+  <si>
+    <t>C4_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_10_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_7_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_14_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_4_N.mzML</t>
+  </si>
+  <si>
+    <t>C4_0_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_6_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_11_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_15_N.mzML</t>
+  </si>
+  <si>
+    <t>C4_4_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_8_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_13_N.mzML</t>
+  </si>
+  <si>
+    <t>C4_3_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_0_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_16_N.mzML</t>
+  </si>
+  <si>
+    <t>C4_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_3_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_12_N.mzML</t>
+  </si>
+  <si>
+    <t>C4_5_N.mzML</t>
+  </si>
+  <si>
+    <t>A4_2_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_17_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_6_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_11_N.mzML</t>
+  </si>
+  <si>
+    <t>C5_0_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_13_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_12_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_18_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_2_N.mzML</t>
+  </si>
+  <si>
+    <t>C5_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_5_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_8_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_0_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_19_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_1_N.mzML</t>
+  </si>
+  <si>
+    <t>C5_4_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_10_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_3_N.mzML</t>
+  </si>
+  <si>
+    <t>C5_3_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_20_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_4_N.mzML</t>
+  </si>
+  <si>
+    <t>C5_5_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_7_N.mzML</t>
+  </si>
+  <si>
+    <t>C5_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A5_9_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_21_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_9_N.mzML</t>
+  </si>
+  <si>
+    <t>C6_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_5_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_4_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_22_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_1_N.mzML</t>
+  </si>
+  <si>
+    <t>C6_0_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_11_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_7_N.mzML</t>
+  </si>
+  <si>
+    <t>C6_4_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_23_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_6_N.mzML</t>
+  </si>
+  <si>
+    <t>C6_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_10_N.mzML</t>
+  </si>
+  <si>
+    <t>C6_5_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_3_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_24_N.mzML</t>
+  </si>
+  <si>
+    <t>C6_3_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_0_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_12_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_8_N.mzML</t>
+  </si>
+  <si>
+    <t>A6_13_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_25_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_8_N.mzML</t>
+  </si>
+  <si>
+    <t>C7_3_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_11_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_4_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_26_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_7_N.mzML</t>
+  </si>
+  <si>
+    <t>C7_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_12_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_6_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_27_N.mzML</t>
+  </si>
+  <si>
+    <t>C7_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_13_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_9_N.mzML</t>
+  </si>
+  <si>
+    <t>C7_0_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_5_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_28_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_3_N.mzML</t>
+  </si>
+  <si>
+    <t>C7_4_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_10_N.mzML</t>
+  </si>
+  <si>
+    <t>A7_0_N.mzML</t>
+  </si>
+  <si>
+    <t>C7_5_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_29_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_6_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_10_N.mzML</t>
+  </si>
+  <si>
+    <t>C8_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_0_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_3_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_30_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_12_N.mzML</t>
+  </si>
+  <si>
+    <t>C8_3_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_4_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_5_N.mzML</t>
+  </si>
+  <si>
+    <t>C8_4_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_31_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_9_N.mzML</t>
+  </si>
+  <si>
+    <t>C8_0_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_7_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_32_N.mzML</t>
+  </si>
+  <si>
+    <t>C8_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_13_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_8_N.mzML</t>
+  </si>
+  <si>
+    <t>C8_5_N.mzML</t>
+  </si>
+  <si>
+    <t>A8_11_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_33_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_2_N.mzML</t>
+  </si>
+  <si>
+    <t>C9_2_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_6_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_8_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_0_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_34_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_5_N.mzML</t>
+  </si>
+  <si>
+    <t>C9_3_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_10_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_13_N.mzML</t>
+  </si>
+  <si>
+    <t>C9_1_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_35_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_4_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_1_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_11_N.mzML</t>
+  </si>
+  <si>
+    <t>C9_0_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_12_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_36_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_7_N.mzML</t>
+  </si>
+  <si>
+    <t>C9_5_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_3_N.mzML</t>
+  </si>
+  <si>
+    <t>C9_4_N.mzML</t>
+  </si>
+  <si>
+    <t>A9_9_N.mzML</t>
+  </si>
+  <si>
+    <t>QC_37_N.mzML</t>
   </si>
 </sst>
 </file>
@@ -1777,7 +1777,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>443</v>
+        <v>226</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -1792,10 +1792,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>441</v>
+        <v>224</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>442</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -1806,7 +1806,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>402</v>
+        <v>227</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>2</v>
@@ -1829,10 +1829,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1852,10 +1852,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1875,10 +1875,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>351</v>
+        <v>230</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1898,10 +1898,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1921,10 +1921,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>353</v>
+        <v>232</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1944,7 +1944,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>413</v>
+        <v>233</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>2</v>
@@ -1967,10 +1967,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1990,10 +1990,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -2013,10 +2013,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>350</v>
+        <v>236</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2036,10 +2036,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2059,10 +2059,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -2082,7 +2082,7 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>423</v>
+        <v>239</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>2</v>
@@ -2105,10 +2105,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>349</v>
+        <v>240</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2128,10 +2128,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -2151,10 +2151,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2174,10 +2174,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>352</v>
+        <v>243</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2197,10 +2197,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2220,7 +2220,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>432</v>
+        <v>245</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>2</v>
@@ -2243,10 +2243,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2266,10 +2266,10 @@
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>348</v>
+        <v>247</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2289,10 +2289,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -2312,10 +2312,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -2335,10 +2335,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -2358,7 +2358,7 @@
         <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>433</v>
+        <v>251</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>2</v>
@@ -2381,10 +2381,10 @@
         <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2404,10 +2404,10 @@
         <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>357</v>
+        <v>253</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2427,10 +2427,10 @@
         <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -2450,10 +2450,10 @@
         <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2473,10 +2473,10 @@
         <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>354</v>
+        <v>256</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -2496,7 +2496,7 @@
         <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>434</v>
+        <v>257</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>2</v>
@@ -2519,10 +2519,10 @@
         <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -2542,10 +2542,10 @@
         <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -2565,10 +2565,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="s">
-        <v>355</v>
+        <v>260</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -2588,10 +2588,10 @@
         <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -2611,10 +2611,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -2634,7 +2634,7 @@
         <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>435</v>
+        <v>263</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>2</v>
@@ -2657,10 +2657,10 @@
         <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -2680,10 +2680,10 @@
         <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -2703,10 +2703,10 @@
         <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>356</v>
+        <v>266</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -2726,10 +2726,10 @@
         <v>45</v>
       </c>
       <c r="C42" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -2749,10 +2749,10 @@
         <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -2772,7 +2772,7 @@
         <v>47</v>
       </c>
       <c r="C44" t="s">
-        <v>436</v>
+        <v>269</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>2</v>
@@ -2795,10 +2795,10 @@
         <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>358</v>
+        <v>270</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -2818,10 +2818,10 @@
         <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -2841,10 +2841,10 @@
         <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>359</v>
+        <v>272</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -2864,10 +2864,10 @@
         <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -2887,10 +2887,10 @@
         <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -2910,7 +2910,7 @@
         <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>437</v>
+        <v>275</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>2</v>
@@ -2933,10 +2933,10 @@
         <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -2956,10 +2956,10 @@
         <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -2979,10 +2979,10 @@
         <v>56</v>
       </c>
       <c r="C53" t="s">
-        <v>361</v>
+        <v>278</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3002,10 +3002,10 @@
         <v>57</v>
       </c>
       <c r="C54" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -3025,10 +3025,10 @@
         <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -3048,7 +3048,7 @@
         <v>59</v>
       </c>
       <c r="C56" t="s">
-        <v>403</v>
+        <v>281</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>2</v>
@@ -3071,10 +3071,10 @@
         <v>60</v>
       </c>
       <c r="C57" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -3094,10 +3094,10 @@
         <v>61</v>
       </c>
       <c r="C58" t="s">
-        <v>364</v>
+        <v>283</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -3117,10 +3117,10 @@
         <v>62</v>
       </c>
       <c r="C59" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -3140,10 +3140,10 @@
         <v>63</v>
       </c>
       <c r="C60" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -3163,10 +3163,10 @@
         <v>64</v>
       </c>
       <c r="C61" t="s">
-        <v>360</v>
+        <v>286</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -3186,7 +3186,7 @@
         <v>65</v>
       </c>
       <c r="C62" t="s">
-        <v>404</v>
+        <v>287</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>2</v>
@@ -3209,10 +3209,10 @@
         <v>66</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -3232,10 +3232,10 @@
         <v>67</v>
       </c>
       <c r="C64" t="s">
-        <v>363</v>
+        <v>289</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E64">
         <v>1</v>
@@ -3255,10 +3255,10 @@
         <v>68</v>
       </c>
       <c r="C65" t="s">
-        <v>251</v>
+        <v>290</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -3278,10 +3278,10 @@
         <v>69</v>
       </c>
       <c r="C66" t="s">
-        <v>253</v>
+        <v>291</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -3301,10 +3301,10 @@
         <v>70</v>
       </c>
       <c r="C67" t="s">
-        <v>365</v>
+        <v>292</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E67">
         <v>1</v>
@@ -3324,7 +3324,7 @@
         <v>71</v>
       </c>
       <c r="C68" t="s">
-        <v>405</v>
+        <v>293</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>2</v>
@@ -3347,10 +3347,10 @@
         <v>72</v>
       </c>
       <c r="C69" t="s">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -3370,10 +3370,10 @@
         <v>73</v>
       </c>
       <c r="C70" t="s">
-        <v>362</v>
+        <v>295</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -3393,10 +3393,10 @@
         <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -3416,10 +3416,10 @@
         <v>75</v>
       </c>
       <c r="C72" t="s">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -3439,10 +3439,10 @@
         <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -3462,7 +3462,7 @@
         <v>77</v>
       </c>
       <c r="C74" t="s">
-        <v>406</v>
+        <v>299</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>2</v>
@@ -3485,10 +3485,10 @@
         <v>78</v>
       </c>
       <c r="C75" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -3508,10 +3508,10 @@
         <v>79</v>
       </c>
       <c r="C76" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E76">
         <v>1</v>
@@ -3531,10 +3531,10 @@
         <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>367</v>
+        <v>302</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E77">
         <v>1</v>
@@ -3554,10 +3554,10 @@
         <v>81</v>
       </c>
       <c r="C78" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -3577,10 +3577,10 @@
         <v>82</v>
       </c>
       <c r="C79" t="s">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E79">
         <v>1</v>
@@ -3600,7 +3600,7 @@
         <v>83</v>
       </c>
       <c r="C80" t="s">
-        <v>407</v>
+        <v>305</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>2</v>
@@ -3623,10 +3623,10 @@
         <v>84</v>
       </c>
       <c r="C81" t="s">
-        <v>265</v>
+        <v>306</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E81">
         <v>1</v>
@@ -3646,10 +3646,10 @@
         <v>85</v>
       </c>
       <c r="C82" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E82">
         <v>1</v>
@@ -3669,10 +3669,10 @@
         <v>86</v>
       </c>
       <c r="C83" t="s">
-        <v>366</v>
+        <v>308</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E83">
         <v>1</v>
@@ -3692,10 +3692,10 @@
         <v>87</v>
       </c>
       <c r="C84" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E84">
         <v>1</v>
@@ -3715,10 +3715,10 @@
         <v>88</v>
       </c>
       <c r="C85" t="s">
-        <v>267</v>
+        <v>310</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E85">
         <v>1</v>
@@ -3738,7 +3738,7 @@
         <v>89</v>
       </c>
       <c r="C86" t="s">
-        <v>408</v>
+        <v>311</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>2</v>
@@ -3761,10 +3761,10 @@
         <v>90</v>
       </c>
       <c r="C87" t="s">
-        <v>370</v>
+        <v>312</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E87">
         <v>1</v>
@@ -3784,10 +3784,10 @@
         <v>91</v>
       </c>
       <c r="C88" t="s">
-        <v>276</v>
+        <v>313</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E88">
         <v>1</v>
@@ -3807,10 +3807,10 @@
         <v>92</v>
       </c>
       <c r="C89" t="s">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E89">
         <v>1</v>
@@ -3830,10 +3830,10 @@
         <v>93</v>
       </c>
       <c r="C90" t="s">
-        <v>369</v>
+        <v>315</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E90">
         <v>1</v>
@@ -3853,10 +3853,10 @@
         <v>94</v>
       </c>
       <c r="C91" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E91">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>95</v>
       </c>
       <c r="C92" t="s">
-        <v>409</v>
+        <v>317</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>2</v>
@@ -3899,10 +3899,10 @@
         <v>96</v>
       </c>
       <c r="C93" t="s">
-        <v>368</v>
+        <v>318</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E93">
         <v>1</v>
@@ -3922,10 +3922,10 @@
         <v>97</v>
       </c>
       <c r="C94" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -3945,10 +3945,10 @@
         <v>98</v>
       </c>
       <c r="C95" t="s">
-        <v>268</v>
+        <v>320</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -3968,10 +3968,10 @@
         <v>99</v>
       </c>
       <c r="C96" t="s">
-        <v>371</v>
+        <v>321</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E96">
         <v>1</v>
@@ -3991,10 +3991,10 @@
         <v>100</v>
       </c>
       <c r="C97" t="s">
-        <v>270</v>
+        <v>322</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -4014,7 +4014,7 @@
         <v>101</v>
       </c>
       <c r="C98" t="s">
-        <v>410</v>
+        <v>323</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>2</v>
@@ -4037,10 +4037,10 @@
         <v>102</v>
       </c>
       <c r="C99" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -4060,10 +4060,10 @@
         <v>103</v>
       </c>
       <c r="C100" t="s">
-        <v>281</v>
+        <v>325</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -4083,10 +4083,10 @@
         <v>104</v>
       </c>
       <c r="C101" t="s">
-        <v>372</v>
+        <v>326</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E101">
         <v>1</v>
@@ -4106,10 +4106,10 @@
         <v>105</v>
       </c>
       <c r="C102" t="s">
-        <v>283</v>
+        <v>327</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E102">
         <v>1</v>
@@ -4129,10 +4129,10 @@
         <v>106</v>
       </c>
       <c r="C103" t="s">
-        <v>282</v>
+        <v>328</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E103">
         <v>1</v>
@@ -4152,7 +4152,7 @@
         <v>107</v>
       </c>
       <c r="C104" t="s">
-        <v>411</v>
+        <v>329</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>2</v>
@@ -4175,10 +4175,10 @@
         <v>108</v>
       </c>
       <c r="C105" t="s">
-        <v>284</v>
+        <v>330</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E105">
         <v>1</v>
@@ -4198,10 +4198,10 @@
         <v>109</v>
       </c>
       <c r="C106" t="s">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E106">
         <v>1</v>
@@ -4221,10 +4221,10 @@
         <v>110</v>
       </c>
       <c r="C107" t="s">
-        <v>287</v>
+        <v>332</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E107">
         <v>1</v>
@@ -4244,10 +4244,10 @@
         <v>111</v>
       </c>
       <c r="C108" t="s">
-        <v>290</v>
+        <v>333</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E108">
         <v>1</v>
@@ -4267,10 +4267,10 @@
         <v>112</v>
       </c>
       <c r="C109" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E109">
         <v>1</v>
@@ -4290,7 +4290,7 @@
         <v>113</v>
       </c>
       <c r="C110" t="s">
-        <v>412</v>
+        <v>335</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>2</v>
@@ -4313,10 +4313,10 @@
         <v>114</v>
       </c>
       <c r="C111" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E111">
         <v>1</v>
@@ -4336,10 +4336,10 @@
         <v>115</v>
       </c>
       <c r="C112" t="s">
-        <v>376</v>
+        <v>337</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E112">
         <v>1</v>
@@ -4359,10 +4359,10 @@
         <v>116</v>
       </c>
       <c r="C113" t="s">
-        <v>280</v>
+        <v>338</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E113">
         <v>1</v>
@@ -4382,10 +4382,10 @@
         <v>117</v>
       </c>
       <c r="C114" t="s">
-        <v>285</v>
+        <v>339</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E114">
         <v>1</v>
@@ -4405,10 +4405,10 @@
         <v>118</v>
       </c>
       <c r="C115" t="s">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E115">
         <v>1</v>
@@ -4428,7 +4428,7 @@
         <v>119</v>
       </c>
       <c r="C116" t="s">
-        <v>414</v>
+        <v>341</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>2</v>
@@ -4451,10 +4451,10 @@
         <v>120</v>
       </c>
       <c r="C117" t="s">
-        <v>286</v>
+        <v>342</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E117">
         <v>1</v>
@@ -4474,10 +4474,10 @@
         <v>121</v>
       </c>
       <c r="C118" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -4497,10 +4497,10 @@
         <v>122</v>
       </c>
       <c r="C119" t="s">
-        <v>289</v>
+        <v>344</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E119">
         <v>1</v>
@@ -4520,10 +4520,10 @@
         <v>123</v>
       </c>
       <c r="C120" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E120">
         <v>1</v>
@@ -4543,10 +4543,10 @@
         <v>124</v>
       </c>
       <c r="C121" t="s">
-        <v>291</v>
+        <v>346</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -4566,7 +4566,7 @@
         <v>125</v>
       </c>
       <c r="C122" t="s">
-        <v>415</v>
+        <v>347</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>2</v>
@@ -4589,10 +4589,10 @@
         <v>126</v>
       </c>
       <c r="C123" t="s">
-        <v>305</v>
+        <v>348</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -4612,10 +4612,10 @@
         <v>127</v>
       </c>
       <c r="C124" t="s">
-        <v>380</v>
+        <v>349</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E124">
         <v>1</v>
@@ -4635,10 +4635,10 @@
         <v>128</v>
       </c>
       <c r="C125" t="s">
-        <v>298</v>
+        <v>350</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E125">
         <v>1</v>
@@ -4658,10 +4658,10 @@
         <v>129</v>
       </c>
       <c r="C126" t="s">
-        <v>301</v>
+        <v>351</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E126">
         <v>1</v>
@@ -4681,10 +4681,10 @@
         <v>130</v>
       </c>
       <c r="C127" t="s">
-        <v>300</v>
+        <v>352</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E127">
         <v>1</v>
@@ -4704,7 +4704,7 @@
         <v>131</v>
       </c>
       <c r="C128" t="s">
-        <v>416</v>
+        <v>353</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>2</v>
@@ -4727,10 +4727,10 @@
         <v>132</v>
       </c>
       <c r="C129" t="s">
-        <v>293</v>
+        <v>354</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E129">
         <v>1</v>
@@ -4750,10 +4750,10 @@
         <v>133</v>
       </c>
       <c r="C130" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E130">
         <v>1</v>
@@ -4773,10 +4773,10 @@
         <v>134</v>
       </c>
       <c r="C131" t="s">
-        <v>295</v>
+        <v>356</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E131">
         <v>1</v>
@@ -4796,10 +4796,10 @@
         <v>135</v>
       </c>
       <c r="C132" t="s">
-        <v>303</v>
+        <v>357</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E132">
         <v>1</v>
@@ -4819,10 +4819,10 @@
         <v>136</v>
       </c>
       <c r="C133" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -4842,7 +4842,7 @@
         <v>137</v>
       </c>
       <c r="C134" t="s">
-        <v>417</v>
+        <v>359</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>2</v>
@@ -4865,10 +4865,10 @@
         <v>138</v>
       </c>
       <c r="C135" t="s">
-        <v>302</v>
+        <v>360</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -4888,10 +4888,10 @@
         <v>139</v>
       </c>
       <c r="C136" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -4911,10 +4911,10 @@
         <v>140</v>
       </c>
       <c r="C137" t="s">
-        <v>294</v>
+        <v>362</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -4934,10 +4934,10 @@
         <v>141</v>
       </c>
       <c r="C138" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -4957,10 +4957,10 @@
         <v>142</v>
       </c>
       <c r="C139" t="s">
-        <v>299</v>
+        <v>364</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -4980,7 +4980,7 @@
         <v>143</v>
       </c>
       <c r="C140" t="s">
-        <v>418</v>
+        <v>365</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>2</v>
@@ -5003,10 +5003,10 @@
         <v>144</v>
       </c>
       <c r="C141" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E141">
         <v>1</v>
@@ -5026,10 +5026,10 @@
         <v>145</v>
       </c>
       <c r="C142" t="s">
-        <v>292</v>
+        <v>367</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E142">
         <v>1</v>
@@ -5049,10 +5049,10 @@
         <v>146</v>
       </c>
       <c r="C143" t="s">
-        <v>296</v>
+        <v>368</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E143">
         <v>1</v>
@@ -5072,10 +5072,10 @@
         <v>147</v>
       </c>
       <c r="C144" t="s">
-        <v>304</v>
+        <v>369</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -5095,10 +5095,10 @@
         <v>148</v>
       </c>
       <c r="C145" t="s">
-        <v>297</v>
+        <v>370</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E145">
         <v>1</v>
@@ -5118,7 +5118,7 @@
         <v>149</v>
       </c>
       <c r="C146" t="s">
-        <v>419</v>
+        <v>371</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>2</v>
@@ -5141,10 +5141,10 @@
         <v>150</v>
       </c>
       <c r="C147" t="s">
-        <v>312</v>
+        <v>372</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -5164,10 +5164,10 @@
         <v>151</v>
       </c>
       <c r="C148" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E148">
         <v>1</v>
@@ -5187,10 +5187,10 @@
         <v>152</v>
       </c>
       <c r="C149" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E149">
         <v>1</v>
@@ -5210,10 +5210,10 @@
         <v>153</v>
       </c>
       <c r="C150" t="s">
-        <v>309</v>
+        <v>375</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E150">
         <v>1</v>
@@ -5233,10 +5233,10 @@
         <v>154</v>
       </c>
       <c r="C151" t="s">
-        <v>314</v>
+        <v>376</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -5256,7 +5256,7 @@
         <v>155</v>
       </c>
       <c r="C152" t="s">
-        <v>438</v>
+        <v>377</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>2</v>
@@ -5279,10 +5279,10 @@
         <v>156</v>
       </c>
       <c r="C153" t="s">
-        <v>307</v>
+        <v>378</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E153">
         <v>1</v>
@@ -5302,10 +5302,10 @@
         <v>157</v>
       </c>
       <c r="C154" t="s">
-        <v>317</v>
+        <v>379</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E154">
         <v>1</v>
@@ -5325,10 +5325,10 @@
         <v>158</v>
       </c>
       <c r="C155" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E155">
         <v>1</v>
@@ -5348,10 +5348,10 @@
         <v>159</v>
       </c>
       <c r="C156" t="s">
-        <v>310</v>
+        <v>381</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -5371,10 +5371,10 @@
         <v>160</v>
       </c>
       <c r="C157" t="s">
-        <v>316</v>
+        <v>382</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E157">
         <v>1</v>
@@ -5394,7 +5394,7 @@
         <v>161</v>
       </c>
       <c r="C158" t="s">
-        <v>420</v>
+        <v>383</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>2</v>
@@ -5417,10 +5417,10 @@
         <v>162</v>
       </c>
       <c r="C159" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E159">
         <v>1</v>
@@ -5440,10 +5440,10 @@
         <v>163</v>
       </c>
       <c r="C160" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E160">
         <v>1</v>
@@ -5463,10 +5463,10 @@
         <v>164</v>
       </c>
       <c r="C161" t="s">
-        <v>319</v>
+        <v>386</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E161">
         <v>1</v>
@@ -5486,10 +5486,10 @@
         <v>165</v>
       </c>
       <c r="C162" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E162">
         <v>1</v>
@@ -5509,10 +5509,10 @@
         <v>166</v>
       </c>
       <c r="C163" t="s">
-        <v>315</v>
+        <v>388</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E163">
         <v>1</v>
@@ -5532,7 +5532,7 @@
         <v>167</v>
       </c>
       <c r="C164" t="s">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>2</v>
@@ -5555,10 +5555,10 @@
         <v>168</v>
       </c>
       <c r="C165" t="s">
-        <v>313</v>
+        <v>390</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E165">
         <v>1</v>
@@ -5578,10 +5578,10 @@
         <v>169</v>
       </c>
       <c r="C166" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E166">
         <v>1</v>
@@ -5601,10 +5601,10 @@
         <v>170</v>
       </c>
       <c r="C167" t="s">
-        <v>308</v>
+        <v>392</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -5624,10 +5624,10 @@
         <v>171</v>
       </c>
       <c r="C168" t="s">
-        <v>306</v>
+        <v>393</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E168">
         <v>1</v>
@@ -5647,10 +5647,10 @@
         <v>172</v>
       </c>
       <c r="C169" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E169">
         <v>1</v>
@@ -5670,7 +5670,7 @@
         <v>173</v>
       </c>
       <c r="C170" t="s">
-        <v>422</v>
+        <v>395</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>2</v>
@@ -5693,10 +5693,10 @@
         <v>174</v>
       </c>
       <c r="C171" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E171">
         <v>1</v>
@@ -5716,10 +5716,10 @@
         <v>175</v>
       </c>
       <c r="C172" t="s">
-        <v>322</v>
+        <v>397</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E172">
         <v>1</v>
@@ -5739,10 +5739,10 @@
         <v>176</v>
       </c>
       <c r="C173" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -5762,10 +5762,10 @@
         <v>177</v>
       </c>
       <c r="C174" t="s">
-        <v>320</v>
+        <v>399</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E174">
         <v>1</v>
@@ -5785,10 +5785,10 @@
         <v>178</v>
       </c>
       <c r="C175" t="s">
-        <v>327</v>
+        <v>400</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E175">
         <v>1</v>
@@ -5808,7 +5808,7 @@
         <v>179</v>
       </c>
       <c r="C176" t="s">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>2</v>
@@ -5831,10 +5831,10 @@
         <v>180</v>
       </c>
       <c r="C177" t="s">
-        <v>324</v>
+        <v>402</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E177">
         <v>1</v>
@@ -5854,10 +5854,10 @@
         <v>181</v>
       </c>
       <c r="C178" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E178">
         <v>1</v>
@@ -5877,10 +5877,10 @@
         <v>182</v>
       </c>
       <c r="C179" t="s">
-        <v>328</v>
+        <v>404</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E179">
         <v>1</v>
@@ -5900,10 +5900,10 @@
         <v>183</v>
       </c>
       <c r="C180" t="s">
-        <v>329</v>
+        <v>405</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E180">
         <v>1</v>
@@ -5923,10 +5923,10 @@
         <v>184</v>
       </c>
       <c r="C181" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E181">
         <v>1</v>
@@ -5946,7 +5946,7 @@
         <v>185</v>
       </c>
       <c r="C182" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>2</v>
@@ -5969,10 +5969,10 @@
         <v>186</v>
       </c>
       <c r="C183" t="s">
-        <v>326</v>
+        <v>408</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E183">
         <v>1</v>
@@ -5992,10 +5992,10 @@
         <v>187</v>
       </c>
       <c r="C184" t="s">
-        <v>333</v>
+        <v>409</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E184">
         <v>1</v>
@@ -6015,10 +6015,10 @@
         <v>188</v>
       </c>
       <c r="C185" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E185">
         <v>1</v>
@@ -6038,10 +6038,10 @@
         <v>189</v>
       </c>
       <c r="C186" t="s">
-        <v>321</v>
+        <v>411</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E186">
         <v>1</v>
@@ -6061,10 +6061,10 @@
         <v>190</v>
       </c>
       <c r="C187" t="s">
-        <v>331</v>
+        <v>412</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E187">
         <v>1</v>
@@ -6084,7 +6084,7 @@
         <v>191</v>
       </c>
       <c r="C188" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>2</v>
@@ -6107,10 +6107,10 @@
         <v>192</v>
       </c>
       <c r="C189" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E189">
         <v>1</v>
@@ -6130,10 +6130,10 @@
         <v>193</v>
       </c>
       <c r="C190" t="s">
-        <v>325</v>
+        <v>415</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E190">
         <v>1</v>
@@ -6153,10 +6153,10 @@
         <v>194</v>
       </c>
       <c r="C191" t="s">
-        <v>332</v>
+        <v>416</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E191">
         <v>1</v>
@@ -6176,10 +6176,10 @@
         <v>195</v>
       </c>
       <c r="C192" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E192">
         <v>1</v>
@@ -6199,10 +6199,10 @@
         <v>196</v>
       </c>
       <c r="C193" t="s">
-        <v>323</v>
+        <v>418</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E193">
         <v>1</v>
@@ -6222,7 +6222,7 @@
         <v>197</v>
       </c>
       <c r="C194" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>2</v>
@@ -6245,10 +6245,10 @@
         <v>198</v>
       </c>
       <c r="C195" t="s">
-        <v>340</v>
+        <v>420</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E195">
         <v>1</v>
@@ -6268,10 +6268,10 @@
         <v>199</v>
       </c>
       <c r="C196" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E196">
         <v>1</v>
@@ -6291,10 +6291,10 @@
         <v>200</v>
       </c>
       <c r="C197" t="s">
-        <v>344</v>
+        <v>422</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E197">
         <v>1</v>
@@ -6314,10 +6314,10 @@
         <v>201</v>
       </c>
       <c r="C198" t="s">
-        <v>346</v>
+        <v>423</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E198">
         <v>1</v>
@@ -6337,10 +6337,10 @@
         <v>202</v>
       </c>
       <c r="C199" t="s">
-        <v>334</v>
+        <v>424</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E199">
         <v>1</v>
@@ -6360,7 +6360,7 @@
         <v>203</v>
       </c>
       <c r="C200" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>2</v>
@@ -6383,10 +6383,10 @@
         <v>204</v>
       </c>
       <c r="C201" t="s">
-        <v>343</v>
+        <v>426</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E201">
         <v>1</v>
@@ -6406,10 +6406,10 @@
         <v>205</v>
       </c>
       <c r="C202" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E202">
         <v>1</v>
@@ -6429,10 +6429,10 @@
         <v>206</v>
       </c>
       <c r="C203" t="s">
-        <v>336</v>
+        <v>428</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E203">
         <v>1</v>
@@ -6452,10 +6452,10 @@
         <v>207</v>
       </c>
       <c r="C204" t="s">
-        <v>339</v>
+        <v>429</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E204">
         <v>1</v>
@@ -6475,10 +6475,10 @@
         <v>208</v>
       </c>
       <c r="C205" t="s">
-        <v>397</v>
+        <v>430</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E205">
         <v>1</v>
@@ -6498,7 +6498,7 @@
         <v>209</v>
       </c>
       <c r="C206" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>2</v>
@@ -6521,10 +6521,10 @@
         <v>210</v>
       </c>
       <c r="C207" t="s">
-        <v>342</v>
+        <v>432</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E207">
         <v>1</v>
@@ -6544,10 +6544,10 @@
         <v>211</v>
       </c>
       <c r="C208" t="s">
-        <v>335</v>
+        <v>433</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E208">
         <v>1</v>
@@ -6567,10 +6567,10 @@
         <v>212</v>
       </c>
       <c r="C209" t="s">
-        <v>337</v>
+        <v>434</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E209">
         <v>1</v>
@@ -6590,10 +6590,10 @@
         <v>213</v>
       </c>
       <c r="C210" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E210">
         <v>1</v>
@@ -6613,10 +6613,10 @@
         <v>214</v>
       </c>
       <c r="C211" t="s">
-        <v>338</v>
+        <v>436</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E211">
         <v>1</v>
@@ -6636,7 +6636,7 @@
         <v>215</v>
       </c>
       <c r="C212" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>2</v>
@@ -6659,10 +6659,10 @@
         <v>216</v>
       </c>
       <c r="C213" t="s">
-        <v>345</v>
+        <v>438</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E213">
         <v>1</v>
@@ -6682,10 +6682,10 @@
         <v>217</v>
       </c>
       <c r="C214" t="s">
-        <v>401</v>
+        <v>439</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E214">
         <v>1</v>
@@ -6705,10 +6705,10 @@
         <v>218</v>
       </c>
       <c r="C215" t="s">
-        <v>341</v>
+        <v>440</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E215">
         <v>1</v>
@@ -6728,10 +6728,10 @@
         <v>219</v>
       </c>
       <c r="C216" t="s">
-        <v>400</v>
+        <v>441</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>440</v>
+        <v>223</v>
       </c>
       <c r="E216">
         <v>1</v>
@@ -6751,10 +6751,10 @@
         <v>220</v>
       </c>
       <c r="C217" t="s">
-        <v>347</v>
+        <v>442</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>439</v>
+        <v>222</v>
       </c>
       <c r="E217">
         <v>1</v>
@@ -6774,7 +6774,7 @@
         <v>221</v>
       </c>
       <c r="C218" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>2</v>
